--- a/ig/ch-elm/StructureDefinition-ch-elm-coding.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-coding.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/StructureDefinition/Coding-uv-ips</t>
+    <t>http://hl7.org/fhir/uv/ips/StructureDefinition/Coding-uv-ips|2.0.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -427,7 +427,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>Representation defined by the system</t>
+    <t>Text representation defined by the system</t>
   </si>
   <si>
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
@@ -469,14 +469,14 @@
     <t>translation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {translation}
+    <t xml:space="preserve">Extension {translation|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
     <t>Language Translation (Localization)</t>
   </si>
   <si>
-    <t>Language translation from base language of resource to another language.</t>
+    <t>Language translation from base language of resource to another language, used to provide translations for strings, including markdown. Generally, the type of the translation extension SHOULD match that of the element being extended.</t>
   </si>
   <si>
     <t>ST.translation</t>
@@ -854,7 +854,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="19.5625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="32.1171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1669,7 +1669,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>132</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>90</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>77</v>

--- a/ig/ch-elm/StructureDefinition-ch-elm-coding.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-coding.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-coding.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-coding.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-coding.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-coding.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
